--- a/error_log.xlsx
+++ b/error_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4072,6 +4072,77 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Mananow.py</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Missing 'Comment' field in JSON object.</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>584</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2025-05-20 19:54:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Manachat.py</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Failed to load mental health model: mentall/mental-roberta-base is not a local folder and is not a valid model identifier listed on 'https://huggingface.co/models'
+If this is a private repository, make sure to pass a token having permission to this repo either by logging in with `huggingface-cli login` or by passing `token=&lt;your_token&gt;`</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>73</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2025-05-24 01:05:44</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
